--- a/14_stocks_analysis/01_rankings_sector/2604_software.xlsx
+++ b/14_stocks_analysis/01_rankings_sector/2604_software.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ebc00a0f969ad489/Programmazione/github/FromZeroToQuant-/14_stocks_analysis/01_rankings_sector/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5919C4BC-6348-4657-AF99-6899CF912A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{5919C4BC-6348-4657-AF99-6899CF912A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1862BF61-9B7B-48EC-9486-353E8E223A49}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{586D3EA5-9D9A-4272-8C2C-33115CD852C0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="312">
   <si>
     <t>Symbol</t>
   </si>
@@ -71,12 +71,6 @@
     <t>ADBE</t>
   </si>
   <si>
-    <t>92.39B</t>
-  </si>
-  <si>
-    <t>+110.49</t>
-  </si>
-  <si>
     <t>7.53</t>
   </si>
   <si>
@@ -95,12 +89,6 @@
     <t>QLYS</t>
   </si>
   <si>
-    <t>2.75B</t>
-  </si>
-  <si>
-    <t>+93.04</t>
-  </si>
-  <si>
     <t>6.67</t>
   </si>
   <si>
@@ -113,12 +101,6 @@
     <t>IMXI</t>
   </si>
   <si>
-    <t>473.62M</t>
-  </si>
-  <si>
-    <t>+31.10</t>
-  </si>
-  <si>
     <t>4.08</t>
   </si>
   <si>
@@ -131,12 +113,6 @@
     <t>4704.T</t>
   </si>
   <si>
-    <t>4.24B</t>
-  </si>
-  <si>
-    <t>+88.57</t>
-  </si>
-  <si>
     <t>3.34</t>
   </si>
   <si>
@@ -152,15 +128,6 @@
     <t>WEX</t>
   </si>
   <si>
-    <t>5.65B</t>
-  </si>
-  <si>
-    <t>+61.91</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
     <t>5.0</t>
   </si>
   <si>
@@ -173,12 +140,6 @@
     <t>RDVT</t>
   </si>
   <si>
-    <t>498.59M</t>
-  </si>
-  <si>
-    <t>+59.74</t>
-  </si>
-  <si>
     <t>45.13</t>
   </si>
   <si>
@@ -194,12 +155,6 @@
     <t>DBX</t>
   </si>
   <si>
-    <t>5.92B</t>
-  </si>
-  <si>
-    <t>+47.96</t>
-  </si>
-  <si>
     <t>0.47</t>
   </si>
   <si>
@@ -212,12 +167,6 @@
     <t>DOCN</t>
   </si>
   <si>
-    <t>6.92B</t>
-  </si>
-  <si>
-    <t>+44.07</t>
-  </si>
-  <si>
     <t>2.03</t>
   </si>
   <si>
@@ -233,12 +182,6 @@
     <t>YOU</t>
   </si>
   <si>
-    <t>4.41B</t>
-  </si>
-  <si>
-    <t>+40.03</t>
-  </si>
-  <si>
     <t>3.12</t>
   </si>
   <si>
@@ -248,12 +191,6 @@
     <t>VTEX</t>
   </si>
   <si>
-    <t>746.67M</t>
-  </si>
-  <si>
-    <t>+25.56</t>
-  </si>
-  <si>
     <t>4.82</t>
   </si>
   <si>
@@ -266,12 +203,6 @@
     <t>IDCC</t>
   </si>
   <si>
-    <t>9.09B</t>
-  </si>
-  <si>
-    <t>-14.49</t>
-  </si>
-  <si>
     <t>8.06</t>
   </si>
   <si>
@@ -284,12 +215,6 @@
     <t>PAYC</t>
   </si>
   <si>
-    <t>6.34B</t>
-  </si>
-  <si>
-    <t>+100.46</t>
-  </si>
-  <si>
     <t>1.92</t>
   </si>
   <si>
@@ -305,12 +230,6 @@
     <t>SAP.DE</t>
   </si>
   <si>
-    <t>190.55B</t>
-  </si>
-  <si>
-    <t>+68.33</t>
-  </si>
-  <si>
     <t>7.63</t>
   </si>
   <si>
@@ -326,12 +245,6 @@
     <t>OTEX.TO</t>
   </si>
   <si>
-    <t>5.25B</t>
-  </si>
-  <si>
-    <t>+82.48</t>
-  </si>
-  <si>
     <t>1.51</t>
   </si>
   <si>
@@ -344,12 +257,6 @@
     <t>RAMP</t>
   </si>
   <si>
-    <t>1.64B</t>
-  </si>
-  <si>
-    <t>+80.16</t>
-  </si>
-  <si>
     <t>3.87</t>
   </si>
   <si>
@@ -362,12 +269,6 @@
     <t>GDDY</t>
   </si>
   <si>
-    <t>10.74B</t>
-  </si>
-  <si>
-    <t>+58.12</t>
-  </si>
-  <si>
     <t>1.71</t>
   </si>
   <si>
@@ -380,12 +281,6 @@
     <t>SGE.L</t>
   </si>
   <si>
-    <t>10.76B</t>
-  </si>
-  <si>
-    <t>+45.24</t>
-  </si>
-  <si>
     <t>3.38</t>
   </si>
   <si>
@@ -398,18 +293,6 @@
     <t>ADSK</t>
   </si>
   <si>
-    <t>46.53B</t>
-  </si>
-  <si>
-    <t>+40.11</t>
-  </si>
-  <si>
-    <t>11.48</t>
-  </si>
-  <si>
-    <t>-1.87</t>
-  </si>
-  <si>
     <t>CSG Systems International, Inc.</t>
   </si>
   <si>
@@ -419,9 +302,6 @@
     <t>2.22B</t>
   </si>
   <si>
-    <t>+33.32</t>
-  </si>
-  <si>
     <t>3.61</t>
   </si>
   <si>
@@ -434,12 +314,6 @@
     <t>ACIW</t>
   </si>
   <si>
-    <t>4.15B</t>
-  </si>
-  <si>
-    <t>+31.16</t>
-  </si>
-  <si>
     <t>3.77</t>
   </si>
   <si>
@@ -452,30 +326,12 @@
     <t>4684.T</t>
   </si>
   <si>
-    <t>10.69B</t>
-  </si>
-  <si>
-    <t>+27.97</t>
-  </si>
-  <si>
-    <t>17.91</t>
-  </si>
-  <si>
-    <t>-2.44</t>
-  </si>
-  <si>
     <t>Marqeta, Inc.</t>
   </si>
   <si>
     <t>MQ</t>
   </si>
   <si>
-    <t>1.78B</t>
-  </si>
-  <si>
-    <t>+21.30</t>
-  </si>
-  <si>
     <t>1.67</t>
   </si>
   <si>
@@ -488,12 +344,6 @@
     <t>EVCM</t>
   </si>
   <si>
-    <t>1.98B</t>
-  </si>
-  <si>
-    <t>+7.05</t>
-  </si>
-  <si>
     <t>-2.58</t>
   </si>
   <si>
@@ -503,12 +353,6 @@
     <t>FFIV</t>
   </si>
   <si>
-    <t>16.71B</t>
-  </si>
-  <si>
-    <t>+4.74</t>
-  </si>
-  <si>
     <t>5.07</t>
   </si>
   <si>
@@ -521,12 +365,6 @@
     <t>PLUS</t>
   </si>
   <si>
-    <t>2.13B</t>
-  </si>
-  <si>
-    <t>+4.13</t>
-  </si>
-  <si>
     <t>4.60</t>
   </si>
   <si>
@@ -539,12 +377,6 @@
     <t>DBD</t>
   </si>
   <si>
-    <t>3.12B</t>
-  </si>
-  <si>
-    <t>-32.12</t>
-  </si>
-  <si>
     <t>1.90</t>
   </si>
   <si>
@@ -557,30 +389,12 @@
     <t>INTU</t>
   </si>
   <si>
-    <t>97.91B</t>
-  </si>
-  <si>
-    <t>+107.88</t>
-  </si>
-  <si>
-    <t>7.39</t>
-  </si>
-  <si>
-    <t>-2.24</t>
-  </si>
-  <si>
     <t>Serko Limited</t>
   </si>
   <si>
     <t>SKO.NZ</t>
   </si>
   <si>
-    <t>130.90M</t>
-  </si>
-  <si>
-    <t>+170.49</t>
-  </si>
-  <si>
     <t>10.06</t>
   </si>
   <si>
@@ -596,12 +410,6 @@
     <t>OSPN</t>
   </si>
   <si>
-    <t>401.72M</t>
-  </si>
-  <si>
-    <t>+32.17</t>
-  </si>
-  <si>
     <t>4.25</t>
   </si>
   <si>
@@ -614,12 +422,6 @@
     <t>HUBS</t>
   </si>
   <si>
-    <t>10.08B</t>
-  </si>
-  <si>
-    <t>+96.76</t>
-  </si>
-  <si>
     <t>7.91</t>
   </si>
   <si>
@@ -632,12 +434,6 @@
     <t>PTC</t>
   </si>
   <si>
-    <t>15.92B</t>
-  </si>
-  <si>
-    <t>+85.85</t>
-  </si>
-  <si>
     <t>6.36</t>
   </si>
   <si>
@@ -650,12 +446,6 @@
     <t>WK</t>
   </si>
   <si>
-    <t>2.95B</t>
-  </si>
-  <si>
-    <t>+70.42</t>
-  </si>
-  <si>
     <t>2.09</t>
   </si>
   <si>
@@ -668,48 +458,18 @@
     <t>EEFT</t>
   </si>
   <si>
-    <t>3.14B</t>
-  </si>
-  <si>
-    <t>+54.60</t>
-  </si>
-  <si>
     <t>1.89</t>
   </si>
   <si>
     <t>-2.53</t>
   </si>
   <si>
-    <t>Fortinet, Inc.</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>57.00B</t>
-  </si>
-  <si>
-    <t>+24.12</t>
-  </si>
-  <si>
-    <t>5.22</t>
-  </si>
-  <si>
-    <t>-2.23</t>
-  </si>
-  <si>
     <t>Commvault Systems, Inc.</t>
   </si>
   <si>
     <t>CVLT</t>
   </si>
   <si>
-    <t>3.92B</t>
-  </si>
-  <si>
-    <t>+15.93</t>
-  </si>
-  <si>
     <t>15.63</t>
   </si>
   <si>
@@ -722,12 +482,6 @@
     <t>VRSN</t>
   </si>
   <si>
-    <t>24.29B</t>
-  </si>
-  <si>
-    <t>+8.99</t>
-  </si>
-  <si>
     <t>-5.09</t>
   </si>
   <si>
@@ -740,117 +494,33 @@
     <t>PEGA</t>
   </si>
   <si>
-    <t>6.72B</t>
-  </si>
-  <si>
-    <t>+169.55</t>
-  </si>
-  <si>
-    <t>9.42</t>
-  </si>
-  <si>
-    <t>-1.68</t>
-  </si>
-  <si>
     <t>Fair Isaac Corporation</t>
   </si>
   <si>
     <t>FICO</t>
   </si>
   <si>
-    <t>21.88B</t>
-  </si>
-  <si>
-    <t>+72.34</t>
-  </si>
-  <si>
     <t>12.95</t>
   </si>
   <si>
-    <t>eGain Corporation</t>
-  </si>
-  <si>
-    <t>EGAN</t>
-  </si>
-  <si>
-    <t>196.28M</t>
-  </si>
-  <si>
-    <t>+9.00</t>
-  </si>
-  <si>
-    <t>1.35</t>
-  </si>
-  <si>
-    <t>-2.94</t>
-  </si>
-  <si>
-    <t>Calix, Inc.</t>
-  </si>
-  <si>
-    <t>CALX</t>
-  </si>
-  <si>
-    <t>3.19B</t>
-  </si>
-  <si>
-    <t>+4.69</t>
-  </si>
-  <si>
-    <t>11.76</t>
-  </si>
-  <si>
-    <t>-2.76</t>
-  </si>
-  <si>
     <t>NICE Ltd.</t>
   </si>
   <si>
     <t>NICE.TA</t>
   </si>
   <si>
-    <t>6.81B</t>
-  </si>
-  <si>
-    <t>+103.86</t>
-  </si>
-  <si>
     <t>4.64</t>
   </si>
   <si>
     <t>-2.47</t>
   </si>
   <si>
-    <t>Manhattan Associates, Inc.</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>7.31B</t>
-  </si>
-  <si>
-    <t>+65.56</t>
-  </si>
-  <si>
-    <t>15.14</t>
-  </si>
-  <si>
-    <t>-3.06</t>
-  </si>
-  <si>
     <t>The Trade Desk, Inc.</t>
   </si>
   <si>
     <t>TTD</t>
   </si>
   <si>
-    <t>9.64B</t>
-  </si>
-  <si>
-    <t>+182.43</t>
-  </si>
-  <si>
     <t>4.02</t>
   </si>
   <si>
@@ -863,54 +533,12 @@
     <t>ZM</t>
   </si>
   <si>
-    <t>23.81B</t>
-  </si>
-  <si>
-    <t>+96.44</t>
-  </si>
-  <si>
     <t>9.83</t>
   </si>
   <si>
     <t>-2.15</t>
   </si>
   <si>
-    <t>Workday, Inc.</t>
-  </si>
-  <si>
-    <t>WDAY</t>
-  </si>
-  <si>
-    <t>29.39B</t>
-  </si>
-  <si>
-    <t>+67.87</t>
-  </si>
-  <si>
-    <t>3.46</t>
-  </si>
-  <si>
-    <t>-2.20</t>
-  </si>
-  <si>
-    <t>Dassault Systèmes SE</t>
-  </si>
-  <si>
-    <t>DSY.PA</t>
-  </si>
-  <si>
-    <t>25.98B</t>
-  </si>
-  <si>
-    <t>+67.00</t>
-  </si>
-  <si>
-    <t>3.92</t>
-  </si>
-  <si>
-    <t>-2.12</t>
-  </si>
-  <si>
     <t>ON24, Inc.</t>
   </si>
   <si>
@@ -935,12 +563,6 @@
     <t>SPSC</t>
   </si>
   <si>
-    <t>1.95B</t>
-  </si>
-  <si>
-    <t>+155.43</t>
-  </si>
-  <si>
     <t>11.94</t>
   </si>
   <si>
@@ -950,12 +572,6 @@
     <t>PRTH</t>
   </si>
   <si>
-    <t>371.06M</t>
-  </si>
-  <si>
-    <t>+122.15</t>
-  </si>
-  <si>
     <t>0.69</t>
   </si>
   <si>
@@ -968,13 +584,394 @@
     <t>KXS.TO</t>
   </si>
   <si>
-    <t>2.73B</t>
-  </si>
-  <si>
-    <t>+117.96</t>
-  </si>
-  <si>
     <t>11.33</t>
+  </si>
+  <si>
+    <t>104.94B</t>
+  </si>
+  <si>
+    <t>+85.34</t>
+  </si>
+  <si>
+    <t>3.21B</t>
+  </si>
+  <si>
+    <t>+65.82</t>
+  </si>
+  <si>
+    <t>475.72M</t>
+  </si>
+  <si>
+    <t>+30.52</t>
+  </si>
+  <si>
+    <t>4.75B</t>
+  </si>
+  <si>
+    <t>+67.96</t>
+  </si>
+  <si>
+    <t>5.91B</t>
+  </si>
+  <si>
+    <t>+63.84</t>
+  </si>
+  <si>
+    <t>8.74B</t>
+  </si>
+  <si>
+    <t>+14.01</t>
+  </si>
+  <si>
+    <t>5.44B</t>
+  </si>
+  <si>
+    <t>+13.44</t>
+  </si>
+  <si>
+    <t>3.10B</t>
+  </si>
+  <si>
+    <t>-31.65</t>
+  </si>
+  <si>
+    <t>584.36M</t>
+  </si>
+  <si>
+    <t>+36.30</t>
+  </si>
+  <si>
+    <t>6.38B</t>
+  </si>
+  <si>
+    <t>+34.19</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>-2.48</t>
+  </si>
+  <si>
+    <t>787.43M</t>
+  </si>
+  <si>
+    <t>+19.06</t>
+  </si>
+  <si>
+    <t>9.71B</t>
+  </si>
+  <si>
+    <t>-19.96</t>
+  </si>
+  <si>
+    <t>7.28B</t>
+  </si>
+  <si>
+    <t>+74.58</t>
+  </si>
+  <si>
+    <t>196.97B</t>
+  </si>
+  <si>
+    <t>+62.23</t>
+  </si>
+  <si>
+    <t>1.87B</t>
+  </si>
+  <si>
+    <t>+57.52</t>
+  </si>
+  <si>
+    <t>11.97B</t>
+  </si>
+  <si>
+    <t>+41.82</t>
+  </si>
+  <si>
+    <t>3.63B</t>
+  </si>
+  <si>
+    <t>+33.47</t>
+  </si>
+  <si>
+    <t>+32.96</t>
+  </si>
+  <si>
+    <t>6.62B</t>
+  </si>
+  <si>
+    <t>+32.20</t>
+  </si>
+  <si>
+    <t>11.89B</t>
+  </si>
+  <si>
+    <t>+31.74</t>
+  </si>
+  <si>
+    <t>52.73B</t>
+  </si>
+  <si>
+    <t>+23.74</t>
+  </si>
+  <si>
+    <t>6.37</t>
+  </si>
+  <si>
+    <t>-2.13</t>
+  </si>
+  <si>
+    <t>443.79M</t>
+  </si>
+  <si>
+    <t>+19.64</t>
+  </si>
+  <si>
+    <t>4.60B</t>
+  </si>
+  <si>
+    <t>+18.24</t>
+  </si>
+  <si>
+    <t>11.69B</t>
+  </si>
+  <si>
+    <t>+12.73</t>
+  </si>
+  <si>
+    <t>11.84</t>
+  </si>
+  <si>
+    <t>-2.38</t>
+  </si>
+  <si>
+    <t>4.22B</t>
+  </si>
+  <si>
+    <t>+7.79</t>
+  </si>
+  <si>
+    <t>2.07B</t>
+  </si>
+  <si>
+    <t>+4.47</t>
+  </si>
+  <si>
+    <t>2.18B</t>
+  </si>
+  <si>
+    <t>16.78B</t>
+  </si>
+  <si>
+    <t>+76.39</t>
+  </si>
+  <si>
+    <t>17.94B</t>
+  </si>
+  <si>
+    <t>-2.46</t>
+  </si>
+  <si>
+    <t>25.23B</t>
+  </si>
+  <si>
+    <t>+4.93</t>
+  </si>
+  <si>
+    <t>2.25B</t>
+  </si>
+  <si>
+    <t>-1.22</t>
+  </si>
+  <si>
+    <t>6.33B</t>
+  </si>
+  <si>
+    <t>+141.28</t>
+  </si>
+  <si>
+    <t>7.13</t>
+  </si>
+  <si>
+    <t>-3.21</t>
+  </si>
+  <si>
+    <t>2.19B</t>
+  </si>
+  <si>
+    <t>+126.94</t>
+  </si>
+  <si>
+    <t>3.03B</t>
+  </si>
+  <si>
+    <t>+98.19</t>
+  </si>
+  <si>
+    <t>434.90M</t>
+  </si>
+  <si>
+    <t>+89.54</t>
+  </si>
+  <si>
+    <t>SoundThinking, Inc.</t>
+  </si>
+  <si>
+    <t>SSTI</t>
+  </si>
+  <si>
+    <t>86.95M</t>
+  </si>
+  <si>
+    <t>+116.13</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>-2.57</t>
+  </si>
+  <si>
+    <t>113.61B</t>
+  </si>
+  <si>
+    <t>+78.78</t>
+  </si>
+  <si>
+    <t>7.37</t>
+  </si>
+  <si>
+    <t>-1.80</t>
+  </si>
+  <si>
+    <t>23.02B</t>
+  </si>
+  <si>
+    <t>+63.85</t>
+  </si>
+  <si>
+    <t>11.31B</t>
+  </si>
+  <si>
+    <t>+140.83</t>
+  </si>
+  <si>
+    <t>27.62B</t>
+  </si>
+  <si>
+    <t>+69.34</t>
+  </si>
+  <si>
+    <t>122.44M</t>
+  </si>
+  <si>
+    <t>+191.18</t>
+  </si>
+  <si>
+    <t>12.21B</t>
+  </si>
+  <si>
+    <t>+62.53</t>
+  </si>
+  <si>
+    <t>Atlassian Corporation</t>
+  </si>
+  <si>
+    <t>TEAM</t>
+  </si>
+  <si>
+    <t>19.49B</t>
+  </si>
+  <si>
+    <t>+136.02</t>
+  </si>
+  <si>
+    <t>5.29</t>
+  </si>
+  <si>
+    <t>-1.93</t>
+  </si>
+  <si>
+    <t>6.35B</t>
+  </si>
+  <si>
+    <t>+106.08</t>
+  </si>
+  <si>
+    <t>3.15B</t>
+  </si>
+  <si>
+    <t>+59.30</t>
+  </si>
+  <si>
+    <t>Bill.com Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>BILL</t>
+  </si>
+  <si>
+    <t>4.03B</t>
+  </si>
+  <si>
+    <t>+119.41</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>-1.89</t>
+  </si>
+  <si>
+    <t>Paylocity Holding Corporation</t>
+  </si>
+  <si>
+    <t>PCTY</t>
+  </si>
+  <si>
+    <t>5.63B</t>
+  </si>
+  <si>
+    <t>+114.28</t>
+  </si>
+  <si>
+    <t>1.46</t>
+  </si>
+  <si>
+    <t>-2.39</t>
+  </si>
+  <si>
+    <t>Dynatrace, Inc.</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>10.88B</t>
+  </si>
+  <si>
+    <t>+60.43</t>
+  </si>
+  <si>
+    <t>6.81</t>
+  </si>
+  <si>
+    <t>-1.72</t>
+  </si>
+  <si>
+    <t>Blend Labs, Inc.</t>
+  </si>
+  <si>
+    <t>BLND</t>
+  </si>
+  <si>
+    <t>414.32M</t>
+  </si>
+  <si>
+    <t>+29.37</t>
+  </si>
+  <si>
+    <t>-3.28</t>
   </si>
 </sst>
 </file>
@@ -1349,7 +1346,7 @@
   <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="32" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32" bestFit="1" customWidth="1"/>
@@ -1360,31 +1357,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1399,25 +1396,25 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>183</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1430,36 +1427,36 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
       <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
         <v>14</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1467,36 +1464,36 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>187</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>188</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" t="s">
         <v>14</v>
-      </c>
-      <c r="I6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1504,36 +1501,36 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>189</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>190</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I8" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1541,36 +1538,36 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>191</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="H10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="J10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1578,36 +1575,36 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G12" t="s">
         <v>43</v>
       </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="H12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" t="s">
         <v>45</v>
       </c>
-      <c r="E12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>14</v>
-      </c>
-      <c r="I12" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1615,36 +1612,36 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="E14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>196</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H14" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I14" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1652,36 +1649,36 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>197</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>198</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="H16" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="I16" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="J16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1689,36 +1686,36 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>199</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="G18" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="H18" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="I18" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="J18" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1726,36 +1723,36 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="F20" t="s">
-        <v>71</v>
+        <v>202</v>
       </c>
       <c r="G20" t="s">
-        <v>72</v>
+        <v>203</v>
       </c>
       <c r="H20" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I20" t="s">
-        <v>73</v>
+        <v>204</v>
       </c>
       <c r="J20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1763,36 +1760,36 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>205</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="F22" t="s">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="H22" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="J22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1800,36 +1797,36 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="G24" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="H24" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="I24" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="J24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1837,36 +1834,36 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>209</v>
       </c>
       <c r="E26" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="F26" t="s">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="H26" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="I26" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="J26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1874,36 +1871,36 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="E28" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="F28" t="s">
-        <v>97</v>
+        <v>212</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="H28" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I28" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="J28" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>95</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1911,36 +1908,36 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="E30" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="F30" t="s">
-        <v>103</v>
+        <v>214</v>
       </c>
       <c r="G30" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="H30" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="I30" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="J30" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -1948,36 +1945,36 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="E32" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s">
-        <v>109</v>
+        <v>216</v>
       </c>
       <c r="G32" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I32" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="J32" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1985,36 +1982,36 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="D34" t="s">
-        <v>114</v>
+        <v>217</v>
       </c>
       <c r="E34" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="F34" t="s">
-        <v>115</v>
+        <v>218</v>
       </c>
       <c r="G34" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="H34" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I34" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="J34" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2022,36 +2019,36 @@
         <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="E36" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="F36" t="s">
-        <v>121</v>
+        <v>219</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s">
+        <v>60</v>
+      </c>
+      <c r="I36" t="s">
+        <v>89</v>
+      </c>
+      <c r="J36" t="s">
         <v>14</v>
-      </c>
-      <c r="I36" t="s">
-        <v>123</v>
-      </c>
-      <c r="J36" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2059,36 +2056,36 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>124</v>
+        <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>126</v>
+        <v>220</v>
       </c>
       <c r="E38" t="s">
-        <v>124</v>
+        <v>37</v>
       </c>
       <c r="F38" t="s">
-        <v>127</v>
+        <v>221</v>
       </c>
       <c r="G38" t="s">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="H38" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="I38" t="s">
-        <v>129</v>
+        <v>40</v>
       </c>
       <c r="J38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>125</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2096,36 +2093,36 @@
         <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="C40" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="D40" t="s">
-        <v>132</v>
+        <v>222</v>
       </c>
       <c r="E40" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="F40" t="s">
-        <v>133</v>
+        <v>223</v>
       </c>
       <c r="G40" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s">
+        <v>26</v>
+      </c>
+      <c r="I40" t="s">
+        <v>82</v>
+      </c>
+      <c r="J40" t="s">
         <v>14</v>
-      </c>
-      <c r="I40" t="s">
-        <v>135</v>
-      </c>
-      <c r="J40" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2133,36 +2130,36 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="D42" t="s">
-        <v>138</v>
+        <v>224</v>
       </c>
       <c r="E42" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="F42" t="s">
-        <v>139</v>
+        <v>225</v>
       </c>
       <c r="G42" t="s">
-        <v>140</v>
+        <v>226</v>
       </c>
       <c r="H42" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="I42" t="s">
-        <v>141</v>
+        <v>227</v>
       </c>
       <c r="J42" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2170,36 +2167,36 @@
         <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C44" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="D44" t="s">
-        <v>144</v>
+        <v>228</v>
       </c>
       <c r="E44" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="F44" t="s">
-        <v>145</v>
+        <v>229</v>
       </c>
       <c r="G44" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="H44" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I44" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="J44" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2207,36 +2204,36 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="C46" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="D46" t="s">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="E46" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="F46" t="s">
-        <v>151</v>
+        <v>231</v>
       </c>
       <c r="G46" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="H46" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="I46" t="s">
-        <v>152</v>
+        <v>93</v>
       </c>
       <c r="J46" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>149</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2244,36 +2241,36 @@
         <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>153</v>
+        <v>94</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>94</v>
       </c>
       <c r="D48" t="s">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="E48" t="s">
-        <v>153</v>
+        <v>94</v>
       </c>
       <c r="F48" t="s">
-        <v>156</v>
+        <v>233</v>
       </c>
       <c r="G48" t="s">
-        <v>157</v>
+        <v>234</v>
       </c>
       <c r="H48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I48" t="s">
-        <v>158</v>
+        <v>235</v>
       </c>
       <c r="J48" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -2281,36 +2278,36 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="C50" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="D50" t="s">
-        <v>161</v>
+        <v>236</v>
       </c>
       <c r="E50" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="F50" t="s">
-        <v>162</v>
+        <v>237</v>
       </c>
       <c r="G50" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="H50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I50" t="s">
+        <v>145</v>
+      </c>
+      <c r="J50" t="s">
         <v>14</v>
-      </c>
-      <c r="I50" t="s">
-        <v>164</v>
-      </c>
-      <c r="J50" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -2318,36 +2315,36 @@
         <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>165</v>
+        <v>96</v>
       </c>
       <c r="C52" t="s">
-        <v>165</v>
+        <v>96</v>
       </c>
       <c r="D52" t="s">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="E52" t="s">
-        <v>165</v>
+        <v>96</v>
       </c>
       <c r="F52" t="s">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="G52" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="H52" t="s">
+        <v>30</v>
+      </c>
+      <c r="I52" t="s">
+        <v>99</v>
+      </c>
+      <c r="J52" t="s">
         <v>14</v>
-      </c>
-      <c r="I52" t="s">
-        <v>170</v>
-      </c>
-      <c r="J52" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>166</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -2355,36 +2352,36 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>171</v>
+        <v>100</v>
       </c>
       <c r="C54" t="s">
-        <v>171</v>
+        <v>100</v>
       </c>
       <c r="D54" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="E54" t="s">
-        <v>171</v>
+        <v>100</v>
       </c>
       <c r="F54" t="s">
-        <v>174</v>
+        <v>102</v>
       </c>
       <c r="G54" t="s">
-        <v>175</v>
+        <v>43</v>
       </c>
       <c r="H54" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="I54" t="s">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="J54" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>172</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -2392,36 +2389,36 @@
         <v>28</v>
       </c>
       <c r="B56" t="s">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="C56" t="s">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="D56" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="E56" t="s">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="F56" t="s">
-        <v>180</v>
+        <v>242</v>
       </c>
       <c r="G56" t="s">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="H56" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I56" t="s">
-        <v>182</v>
+        <v>133</v>
       </c>
       <c r="J56" t="s">
-        <v>183</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>178</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -2429,36 +2426,36 @@
         <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="C58" t="s">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
-        <v>186</v>
+        <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="F58" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="G58" t="s">
-        <v>188</v>
+        <v>105</v>
       </c>
       <c r="H58" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I58" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="J58" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>185</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -2466,36 +2463,36 @@
         <v>30</v>
       </c>
       <c r="B60" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
       <c r="C60" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
       <c r="D60" t="s">
-        <v>192</v>
+        <v>245</v>
       </c>
       <c r="E60" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
       <c r="F60" t="s">
-        <v>193</v>
+        <v>246</v>
       </c>
       <c r="G60" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="H60" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I60" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="J60" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>191</v>
+        <v>147</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -2503,36 +2500,36 @@
         <v>31</v>
       </c>
       <c r="B62" t="s">
-        <v>196</v>
+        <v>107</v>
       </c>
       <c r="C62" t="s">
-        <v>196</v>
+        <v>107</v>
       </c>
       <c r="D62" t="s">
-        <v>198</v>
+        <v>247</v>
       </c>
       <c r="E62" t="s">
-        <v>196</v>
+        <v>107</v>
       </c>
       <c r="F62" t="s">
-        <v>199</v>
+        <v>248</v>
       </c>
       <c r="G62" t="s">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="H62" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="I62" t="s">
-        <v>201</v>
+        <v>110</v>
       </c>
       <c r="J62" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>197</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -2540,36 +2537,36 @@
         <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="C64" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="D64" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="E64" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="F64" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="G64" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="H64" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I64" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="J64" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -2577,36 +2574,36 @@
         <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>208</v>
+        <v>150</v>
       </c>
       <c r="C66" t="s">
-        <v>208</v>
+        <v>150</v>
       </c>
       <c r="D66" t="s">
-        <v>210</v>
+        <v>249</v>
       </c>
       <c r="E66" t="s">
-        <v>208</v>
+        <v>150</v>
       </c>
       <c r="F66" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
       <c r="G66" t="s">
-        <v>212</v>
+        <v>251</v>
       </c>
       <c r="H66" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I66" t="s">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="J66" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>209</v>
+        <v>151</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -2614,36 +2611,36 @@
         <v>34</v>
       </c>
       <c r="B68" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="C68" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="D68" t="s">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="E68" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="F68" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="G68" t="s">
-        <v>218</v>
+        <v>175</v>
       </c>
       <c r="H68" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I68" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="J68" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -2651,36 +2648,36 @@
         <v>35</v>
       </c>
       <c r="B70" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="C70" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="D70" t="s">
-        <v>222</v>
+        <v>255</v>
       </c>
       <c r="E70" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="F70" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="G70" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="H70" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="I70" t="s">
-        <v>225</v>
+        <v>89</v>
       </c>
       <c r="J70" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -2688,36 +2685,36 @@
         <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="C72" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D72" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="E72" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="F72" t="s">
-        <v>229</v>
+        <v>258</v>
       </c>
       <c r="G72" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="H72" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="I72" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="J72" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -2725,36 +2722,36 @@
         <v>37</v>
       </c>
       <c r="B74" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="C74" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="D74" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="E74" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="F74" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="G74" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="H74" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I74" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="J74" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -2762,36 +2759,36 @@
         <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>238</v>
+        <v>115</v>
       </c>
       <c r="C76" t="s">
-        <v>238</v>
+        <v>115</v>
       </c>
       <c r="D76" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="E76" t="s">
-        <v>238</v>
+        <v>115</v>
       </c>
       <c r="F76" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="G76" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="H76" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="I76" t="s">
-        <v>42</v>
+        <v>268</v>
       </c>
       <c r="J76" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>239</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -2799,36 +2796,36 @@
         <v>39</v>
       </c>
       <c r="B78" t="s">
-        <v>243</v>
+        <v>152</v>
       </c>
       <c r="C78" t="s">
-        <v>243</v>
+        <v>152</v>
       </c>
       <c r="D78" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="E78" t="s">
-        <v>243</v>
+        <v>152</v>
       </c>
       <c r="F78" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="G78" t="s">
-        <v>247</v>
+        <v>154</v>
       </c>
       <c r="H78" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="I78" t="s">
-        <v>248</v>
+        <v>31</v>
       </c>
       <c r="J78" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>244</v>
+        <v>153</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -2836,36 +2833,36 @@
         <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>249</v>
+        <v>159</v>
       </c>
       <c r="C80" t="s">
-        <v>249</v>
+        <v>159</v>
       </c>
       <c r="D80" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="E80" t="s">
-        <v>249</v>
+        <v>159</v>
       </c>
       <c r="F80" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="G80" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="H80" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I80" t="s">
-        <v>254</v>
+        <v>162</v>
       </c>
       <c r="J80" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>250</v>
+        <v>160</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -2873,36 +2870,36 @@
         <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>255</v>
+        <v>163</v>
       </c>
       <c r="C82" t="s">
-        <v>255</v>
+        <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="E82" t="s">
-        <v>255</v>
+        <v>163</v>
       </c>
       <c r="F82" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="G82" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
       <c r="H82" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I82" t="s">
-        <v>260</v>
+        <v>166</v>
       </c>
       <c r="J82" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>256</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -2910,36 +2907,36 @@
         <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>261</v>
+        <v>117</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>117</v>
       </c>
       <c r="D84" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="E84" t="s">
-        <v>261</v>
+        <v>117</v>
       </c>
       <c r="F84" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="G84" t="s">
-        <v>265</v>
+        <v>119</v>
       </c>
       <c r="H84" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I84" t="s">
-        <v>266</v>
+        <v>120</v>
       </c>
       <c r="J84" t="s">
-        <v>49</v>
+        <v>121</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>262</v>
+        <v>118</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -2947,36 +2944,36 @@
         <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>267</v>
+        <v>126</v>
       </c>
       <c r="C86" t="s">
-        <v>267</v>
+        <v>126</v>
       </c>
       <c r="D86" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E86" t="s">
-        <v>267</v>
+        <v>126</v>
       </c>
       <c r="F86" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="G86" t="s">
-        <v>271</v>
+        <v>128</v>
       </c>
       <c r="H86" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I86" t="s">
-        <v>272</v>
+        <v>129</v>
       </c>
       <c r="J86" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>268</v>
+        <v>127</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -2984,36 +2981,36 @@
         <v>44</v>
       </c>
       <c r="B88" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C88" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D88" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E88" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F88" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="G88" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="H88" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I88" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="J88" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -3021,36 +3018,36 @@
         <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>279</v>
+        <v>155</v>
       </c>
       <c r="C90" t="s">
-        <v>279</v>
+        <v>155</v>
       </c>
       <c r="D90" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E90" t="s">
-        <v>279</v>
+        <v>155</v>
       </c>
       <c r="F90" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G90" t="s">
-        <v>283</v>
+        <v>157</v>
       </c>
       <c r="H90" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="I90" t="s">
-        <v>284</v>
+        <v>158</v>
       </c>
       <c r="J90" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>280</v>
+        <v>156</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -3058,36 +3055,36 @@
         <v>46</v>
       </c>
       <c r="B92" t="s">
-        <v>285</v>
+        <v>134</v>
       </c>
       <c r="C92" t="s">
-        <v>285</v>
+        <v>134</v>
       </c>
       <c r="D92" t="s">
         <v>287</v>
       </c>
       <c r="E92" t="s">
-        <v>285</v>
+        <v>134</v>
       </c>
       <c r="F92" t="s">
         <v>288</v>
       </c>
       <c r="G92" t="s">
-        <v>289</v>
+        <v>136</v>
       </c>
       <c r="H92" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I92" t="s">
-        <v>290</v>
+        <v>137</v>
       </c>
       <c r="J92" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>286</v>
+        <v>135</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -3095,36 +3092,36 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
+        <v>289</v>
+      </c>
+      <c r="C94" t="s">
+        <v>289</v>
+      </c>
+      <c r="D94" t="s">
         <v>291</v>
       </c>
-      <c r="C94" t="s">
-        <v>291</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
+        <v>289</v>
+      </c>
+      <c r="F94" t="s">
+        <v>292</v>
+      </c>
+      <c r="G94" t="s">
         <v>293</v>
       </c>
-      <c r="E94" t="s">
-        <v>291</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="H94" t="s">
+        <v>60</v>
+      </c>
+      <c r="I94" t="s">
         <v>294</v>
       </c>
-      <c r="G94" t="s">
-        <v>295</v>
-      </c>
-      <c r="H94" t="s">
-        <v>41</v>
-      </c>
-      <c r="I94" t="s">
-        <v>296</v>
-      </c>
       <c r="J94" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -3132,36 +3129,36 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
+        <v>295</v>
+      </c>
+      <c r="C96" t="s">
+        <v>295</v>
+      </c>
+      <c r="D96" t="s">
         <v>297</v>
       </c>
-      <c r="C96" t="s">
-        <v>297</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
+        <v>295</v>
+      </c>
+      <c r="F96" t="s">
+        <v>298</v>
+      </c>
+      <c r="G96" t="s">
         <v>299</v>
       </c>
-      <c r="E96" t="s">
-        <v>297</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="H96" t="s">
+        <v>60</v>
+      </c>
+      <c r="I96" t="s">
         <v>300</v>
       </c>
-      <c r="G96" t="s">
-        <v>301</v>
-      </c>
-      <c r="H96" t="s">
-        <v>41</v>
-      </c>
-      <c r="I96" t="s">
-        <v>272</v>
-      </c>
       <c r="J96" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -3169,36 +3166,36 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C98" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D98" t="s">
+        <v>303</v>
+      </c>
+      <c r="E98" t="s">
+        <v>301</v>
+      </c>
+      <c r="F98" t="s">
         <v>304</v>
       </c>
-      <c r="E98" t="s">
-        <v>302</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>305</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
+        <v>26</v>
+      </c>
+      <c r="I98" t="s">
         <v>306</v>
       </c>
-      <c r="H98" t="s">
-        <v>34</v>
-      </c>
-      <c r="I98" t="s">
-        <v>307</v>
-      </c>
       <c r="J98" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -3206,36 +3203,36 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C100" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D100" t="s">
+        <v>309</v>
+      </c>
+      <c r="E100" t="s">
+        <v>307</v>
+      </c>
+      <c r="F100" t="s">
         <v>310</v>
       </c>
-      <c r="E100" t="s">
-        <v>308</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
+        <v>293</v>
+      </c>
+      <c r="H100" t="s">
+        <v>60</v>
+      </c>
+      <c r="I100" t="s">
         <v>311</v>
       </c>
-      <c r="G100" t="s">
-        <v>312</v>
-      </c>
-      <c r="H100" t="s">
-        <v>14</v>
-      </c>
-      <c r="I100" t="s">
-        <v>129</v>
-      </c>
       <c r="J100" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
